--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7640" tabRatio="785" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7640" tabRatio="785"/>
   </bookViews>
   <sheets>
     <sheet name="FECHA 1 VS BARRACAS CENTRAL (V)" sheetId="1" r:id="rId1"/>
@@ -24,15 +24,15 @@
     <sheet name="FECHA 11 VS SARMIENTO (L)" sheetId="10" r:id="rId10"/>
     <sheet name="FECHA 12 VS ESTUDIANTES(RC) (V)" sheetId="11" r:id="rId11"/>
     <sheet name="FECHA 13 VS BELGRANO (L)" sheetId="12" r:id="rId12"/>
-    <sheet name="SUDA 1 VS BLOOMING (V)" sheetId="14" r:id="rId13"/>
-    <sheet name="Resumen Estadísticas" sheetId="13" r:id="rId14"/>
+    <sheet name="SUDA 1 VS BLOOMING (V)" sheetId="13" r:id="rId13"/>
+    <sheet name="Resumen Estadísticas" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="434">
   <si>
     <t>Jugador</t>
   </si>
@@ -1255,6 +1255,75 @@
     <t>180</t>
   </si>
   <si>
+    <t>'6/32</t>
+  </si>
+  <si>
+    <t>'4/30</t>
+  </si>
+  <si>
+    <t>'7/9</t>
+  </si>
+  <si>
+    <t>Germán Pezzella</t>
+  </si>
+  <si>
+    <t>'10/18</t>
+  </si>
+  <si>
+    <t>'23/31</t>
+  </si>
+  <si>
+    <t>'29/35</t>
+  </si>
+  <si>
+    <t>'15/23</t>
+  </si>
+  <si>
+    <t>Blooming</t>
+  </si>
+  <si>
+    <t>• Dificultad para retener la pelota</t>
+  </si>
+  <si>
+    <t>64%</t>
+  </si>
+  <si>
+    <t>36%</t>
+  </si>
+  <si>
+    <t>• Poca generación de juego ofensivo</t>
+  </si>
+  <si>
+    <t>Goles esperados (xG)</t>
+  </si>
+  <si>
+    <t>1.17</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>• El equipo jugó sometido demasiado tiempo</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
@@ -1264,73 +1333,7 @@
     <t>Partidos</t>
   </si>
   <si>
-    <t>'6/32</t>
-  </si>
-  <si>
-    <t>'4/30</t>
-  </si>
-  <si>
-    <t>'7/9</t>
-  </si>
-  <si>
-    <t>Germán Pezzella</t>
-  </si>
-  <si>
-    <t>'10/18</t>
-  </si>
-  <si>
-    <t>'23/31</t>
-  </si>
-  <si>
-    <t>'29/35</t>
-  </si>
-  <si>
-    <t>'15/23</t>
-  </si>
-  <si>
-    <t>Blooming</t>
-  </si>
-  <si>
-    <t>• Dificultad para retener la pelota</t>
-  </si>
-  <si>
-    <t>64%</t>
-  </si>
-  <si>
-    <t>36%</t>
-  </si>
-  <si>
-    <t>• Poca generación de juego ofensivo</t>
-  </si>
-  <si>
-    <t>Goles esperados (xG)</t>
-  </si>
-  <si>
-    <t>1.17</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>• El equipo jugó sometido demasiado tiempo</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>411</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>39</t>
+    <t>Resultado</t>
   </si>
 </sst>
 </file>
@@ -1982,6 +1985,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2009,6 +2015,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2036,6 +2045,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -3088,7 +3100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z35"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -4573,6 +4585,17 @@
       </c>
       <c r="D35" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C36" s="4">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4788,7 +4811,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:Z38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -6367,6 +6390,17 @@
       </c>
       <c r="D37" t="s">
         <v>370</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C38" s="4">
+        <v>2</v>
+      </c>
+      <c r="D38" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6581,7 +6615,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -8143,6 +8177,17 @@
       </c>
       <c r="D36" t="s">
         <v>388</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C37" s="4">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -8357,7 +8402,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -9922,6 +9967,17 @@
       </c>
       <c r="D36" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C37" s="4">
+        <v>3</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10136,7 +10192,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z38"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -10268,7 +10324,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="P2">
         <v>18</v>
@@ -10280,7 +10336,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="T2">
         <v>13</v>
@@ -10327,7 +10383,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="I3">
         <v>77</v>
@@ -10466,7 +10522,7 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B5" t="s">
         <v>32</v>
@@ -10588,7 +10644,7 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="P6">
         <v>55</v>
@@ -10908,7 +10964,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="P10">
         <v>74</v>
@@ -10988,7 +11044,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="P11">
         <v>82</v>
@@ -11228,7 +11284,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="P14">
         <v>65</v>
@@ -11520,7 +11576,7 @@
         <v>87</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D21" s="24" t="s">
         <v>89</v>
@@ -11529,7 +11585,7 @@
         <v>245</v>
       </c>
       <c r="F21" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.35">
@@ -11537,24 +11593,24 @@
         <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D22" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F22" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C23" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D23" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F23" t="s">
         <v>248</v>
@@ -11571,7 +11627,7 @@
         <v>108</v>
       </c>
       <c r="F24" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.35">
@@ -11634,7 +11690,7 @@
         <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D30" t="s">
         <v>97</v>
@@ -11667,10 +11723,10 @@
         <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D33" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.35">
@@ -11678,10 +11734,10 @@
         <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D34" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.35">
@@ -11725,7 +11781,18 @@
         <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>432</v>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11956,19 +12023,19 @@
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>0</v>
@@ -11977,7 +12044,7 @@
         <v>22</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>0</v>
@@ -12510,7 +12577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -14009,6 +14076,17 @@
       </c>
       <c r="D36" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C37" s="4">
+        <v>2</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14223,7 +14301,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -15785,6 +15863,17 @@
       </c>
       <c r="D36" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C37" s="4">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15999,7 +16088,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:Z38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -17572,6 +17661,17 @@
       </c>
       <c r="D37" t="s">
         <v>224</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -17786,7 +17886,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -19351,6 +19451,17 @@
       </c>
       <c r="D36" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19565,7 +19676,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -21127,6 +21238,17 @@
       </c>
       <c r="D36" t="s">
         <v>280</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21341,7 +21463,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z35"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -22829,6 +22951,17 @@
       </c>
       <c r="D35" t="s">
         <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C36" s="4">
+        <v>3</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23043,7 +23176,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z35"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -24525,6 +24658,17 @@
       </c>
       <c r="D35" t="s">
         <v>326</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -24739,7 +24883,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="16" style="4" customWidth="1"/>
@@ -26301,6 +26445,17 @@
       </c>
       <c r="D36" t="s">
         <v>345</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -21,6 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUDA 1 VS BLOOMING (V)" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Estadísticas" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-04 F14 VS RACING CLU (V) LPF" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15-04 F2 VS CARABOBO FC (L) CON" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -828,6 +829,95 @@
 </file>
 
 <file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -15715,6 +15805,2223 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" s="27" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" s="27" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" s="27" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" s="27" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" s="27" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" s="27" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" s="27" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" s="27" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" s="27" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'14/21</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'2/9</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>22</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fabricio Bustos</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'6/10</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'49/59</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>33</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>German Pezzella</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'9/13</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>69</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'40/51</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'1/5</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>20</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lautaro Rivero</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'7/8</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>87</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'53/64</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'2/6</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>33</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>100</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Matías Viña</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>76</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'40/49</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>100</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Marcos Acuña</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>66</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'12/15</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>50</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Juan Cruz Meza</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'7/16</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>43</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'39/41</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>50</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Aníbal Moreno</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>72</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'2/6</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>33</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'52/62</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'4/7</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>57</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Juan Fernando Quintero</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>51</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'33/35</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>60</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'3/4</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>75</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kevin Castaño</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'6/10</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>60</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'38/44</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'3/4</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>75</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'6/9</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>66</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'15/16</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>50</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kendry Páez</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>39</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'4/4</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'21/26</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>50</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>100</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fausto Vera</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>18</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'3/3</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'17/18</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Joaquin Freitas</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>90</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'7/16</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>43</v>
+      </c>
+      <c r="J15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'20/26</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>100</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ian Subiabre</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>45</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'1/4</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>25</v>
+      </c>
+      <c r="J16" t="n">
+        <v>11</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'12/19</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>100</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sebastian Driussi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>45</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>'2/9</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>22</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>'11/14</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>Carabobo FC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Baja efectividad en la definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>• Solidez defensiva (Permitió pocos tiros)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J17">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -22,6 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Estadísticas" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-04 F14 VS RACING CLU (V) LPF" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15-04 F2 VS CARABOBO FC (L) CON" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19-04 F15 VS BOCA JUNIO (L) LPF" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -940,6 +941,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -965,6 +969,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -974,6 +981,89 @@
       <col>7</col>
       <colOff>0</colOff>
       <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="3429000"/>
@@ -18022,6 +18112,2112 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" s="27" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" s="27" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" s="27" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" s="27" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" s="27" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" s="27" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" s="27" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" s="27" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" s="27" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'8/12</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'0/4</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gonzalo Montiel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>66</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'47/55</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>33</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lucas Martínez Quarta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'9/13</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>69</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'67/71</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'8/9</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>88</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>50</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Marcos Acuña</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'12/15</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>80</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'51/67</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'5/10</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>50</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'2/9</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>22</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>50</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lautaro Rivero</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>88</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'4/9</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>44</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'51/58</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'5/6</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>83</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aníbal Moreno</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'3/11</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>27</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'50/62</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'11/16</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>68</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'6/13</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>17</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'30/37</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'0/4</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>50</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'3/6</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>50</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kendry Páez</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>57</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'2/7</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>28</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'9/16</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/5</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Juan Cruz Meza</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'4/4</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'17/19</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>100</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Giuliano Galoppo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'4/10</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>40</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'13/15</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>50</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Facundo Colidio</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>90</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'6/10</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'17/23</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>100</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'1/4</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Maximiliano Salas</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>72</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'1/8</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'12/15</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Joaquin Freitas</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>33</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'1/7</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'9/12</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sebastian Driussi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'1/4</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'3/4</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ian Subiabre</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F19" s="30" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>• El rival llegó con facilidad al arco</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Exceso de faltas cometidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J16">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -23,6 +23,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-04 F14 VS RACING CLU (V) LPF" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15-04 F2 VS CARABOBO FC (L) CON" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19-04 F15 VS BOCA JUNIO (L) LPF" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25-04 F16 VS ALDOSIVI (L) LPF" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1008,6 +1009,95 @@
 </file>
 
 <file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -20218,6 +20308,2122 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" s="27" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" s="27" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" s="27" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" s="27" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" s="27" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" s="27" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" s="27" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" s="27" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" s="27" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'6/8</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>33</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gonzalo Montiel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>66</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'56/64</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'2/5</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>40</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lucas Martínez Quarta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'5/7</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>71</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'66/75</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'8/12</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>66</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lautaro Rivero</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'74/81</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'4/7</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>57</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Marcos Acuña</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'10/13</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>76</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'79/88</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>33</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'8/12</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>66</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>66</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aníbal Moreno</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'1/7</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'65/75</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'8/11</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>72</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>80</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'9/14</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>64</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'33/39</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>33</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Giuliano Galoppo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>67</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'3/8</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>37</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'30/36</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'7/8</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>87</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Juan Cruz Meza</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>23</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'14/15</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>100</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lautaro Pereyra</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>66</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'9/10</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>100</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kendry Páez</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'2/5</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'9/9</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>66</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Facundo Colidio</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>90</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'2/6</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>33</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'22/26</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ian Subiabre</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>80</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'3/11</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>27</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'22/32</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'1/8</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>12</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>66</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Maximiliano Salas</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>67</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'1/5</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>20</v>
+      </c>
+      <c r="J15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'8/13</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>100</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Joaquin Freitas</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>33</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'3/3</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F19" s="30" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D20" s="28" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>• Baja efectividad en la definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Buen volumen de tiros al arco</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>• Solidez defensiva (Permitió pocos tiros)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>• Alta precisión en el armado de juego</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J16">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15-04 F2 VS CARABOBO FC (L) CON" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19-04 F15 VS BOCA JUNIO (L) LPF" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25-04 F16 VS ALDOSIVI (L) LPF" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30-04 F3 VS RED BULL BR (V) CON" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1120,6 +1121,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1145,6 +1149,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1154,6 +1161,89 @@
       <col>7</col>
       <colOff>0</colOff>
       <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="3429000"/>
@@ -22424,6 +22514,2240 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" s="27" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" s="27" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" s="27" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" s="27" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" s="27" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" s="27" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" s="27" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" s="27" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" s="27" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'3/13</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'1/11</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gonzalo Montiel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>66</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'32/39</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lucas Martínez Quarta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'4/9</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>44</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'43/48</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>66</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lautaro Rivero</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'3/8</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>37</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'35/37</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'3/4</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>75</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>50</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Marcos Acuña</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'4/11</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>36</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'39/49</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'2/7</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>28</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>50</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aníbal Moreno</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'8/10</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>80</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'50/62</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'2/7</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>28</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>83</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'8/11</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>72</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'35/38</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>66</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Juan Cruz Meza</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'2/7</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>28</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'16/18</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kendry Páez</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'24/25</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>100</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Giuliano Galoppo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>60</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'13/15</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lucas Silva</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'4/4</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>100</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Facundo Colidio</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>90</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'4/8</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>50</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'19/20</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>100</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Maximiliano Salas</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>89</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'9/12</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ian Subiabre</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>45</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'3/8</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>37</v>
+      </c>
+      <c r="J15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'11/16</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Joaquin Freitas</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>33</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>100</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Agustín Ruberto</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• El rival llegó con facilidad al arco</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>• Buen volumen de tiros al arco</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tarjetas rojas</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J17">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -25,6 +25,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19-04 F15 VS BOCA JUNIO (L) LPF" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25-04 F16 VS ALDOSIVI (L) LPF" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30-04 F3 VS RED BULL BR (V) CON" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-05 F9 VS ATLÉTICO TU (L) LPF" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1210,6 +1211,95 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -26858,6 +26948,2206 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" s="27" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" s="27" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" s="27" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" s="27" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" s="27" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" s="27" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" s="27" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" s="27" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" s="27" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'14/17</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Germán Pezzella</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'6/9</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>66</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'87/94</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'5/10</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>50</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lautaro Rivero</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'5/8</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>62</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'72/85</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'3/10</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>30</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Marcos Acuña</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'2/11</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'84/101</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'1/6</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>16</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'8/14</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>57</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>33</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fabricio Bustos</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>89</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'3/6</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'49/56</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aníbal Moreno</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'7/12</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>58</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'87/99</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>66</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>100</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>65</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'10/10</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'48/55</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>33</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Maxi Meza</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'3/4</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'45/54</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>33</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kendry Páez</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'6/13</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>46</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'25/28</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'3/3</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>100</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lautaro Pereyra</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'5/11</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>45</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'20/20</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'4/7</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>57</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Juan Fernando Quintero</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'24/29</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>33</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'5/7</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>71</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Facundo Colidio</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>90</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'3/10</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>30</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'26/30</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>50</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ian Subiabre</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'3/10</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>30</v>
+      </c>
+      <c r="J14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'10/15</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Agustín Ruberto</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>45</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'1/6</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>16</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'10/10</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Maximiliano Salas</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>45</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'3/7</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>42</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'6/8</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>100</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Joaquin Freitas</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>Atlético Tucumán</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Baja efectividad en la definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>• Alta precisión en el armado de juego</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J17">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -26,6 +26,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25-04 F16 VS ALDOSIVI (L) LPF" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30-04 F3 VS RED BULL BR (V) CON" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-05 F9 VS ATLÉTICO TU (L) LPF" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-05 F4 VS CARABOBO FC (V) CON" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1300,6 +1301,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1325,6 +1329,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1350,6 +1357,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1445,6 +1455,86 @@
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -29148,6 +29238,2245 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" s="27" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" s="27" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" s="27" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" s="27" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" s="27" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" s="27" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" s="27" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" s="27" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" s="27" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" s="27" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" s="27" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" s="27" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" s="27" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>86</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'8/14</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'1/7</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>14</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fabricio Bustos</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'6/10</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'52/69</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>50</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Germán Pezzella</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>33</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'45/48</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>33</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Facundo González</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'0/5</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'61/63</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>66</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Matías Viña</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'9/12</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'33/39</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'6/8</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>75</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>100</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Giuliano Galoppo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'5/6</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>83</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'40/43</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lucas Silva</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>79</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'4/7</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>57</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'46/50</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>50</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>66</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>100</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Juan Fernando Quintero</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>79</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>66</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'47/56</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'1/5</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>20</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'8/11</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>72</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'4/4</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>100</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Santiago Lencina</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'20/25</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Maxi Meza</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>60</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'3/9</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>33</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'24/31</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'1/4</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>25</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>50</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Juan Cruz Meza</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'5/6</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lautaro Pereyra</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>66</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'3/6</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>50</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kendry Páez</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'4/4</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Joaquin Freitas</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>72</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'2/8</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'12/17</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Facundo Colidio</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'9/10</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>100</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Maximiliano Salas</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>33</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>'4/5</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>Carabobo FC</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Exceso de faltas cometidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>• Buen volumen de tiros al arco</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>• Solidez defensiva (Permitió pocos tiros)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tarjetas rojas</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J17">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -29,6 +29,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-05 F4 VS CARABOBO FC (V) CON" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-05 8VOS VS SAN LOREN (L) LPF" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-05 4TOS VS GIMNASIA (L) LPF" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-05 SEMI VS ROSARIO C (L) LPF" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1751,6 +1752,95 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -36123,6 +36213,2206 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" s="31" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" s="31" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" s="31" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" s="31" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" s="31" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" s="31" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" s="31" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" s="31" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" s="31" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" s="31" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" s="31" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" s="31" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" s="31" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" s="31" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" s="31" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" s="31" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" s="31" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" s="31" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" s="31" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" s="31" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" s="31" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" s="31" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" s="31" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'5/12</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'5/12</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lucas Martínez Quarta</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>66</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'31/38</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'2/5</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>40</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lautaro Rivero</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'5/7</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>71</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'33/37</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'3/7</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>42</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Matías Viña</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>83</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'6/8</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>75</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'20/27</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>50</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>33</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>100</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gonzalo Montiel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'25/33</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>50</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fabricio Bustos</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>45</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'20/24</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>50</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Marcos Acuña</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>100</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Germán Pezzella</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Juan Cruz Meza</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'26/33</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'2/9</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>22</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>33</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>33</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fausto Vera</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'5/13</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>38</v>
+      </c>
+      <c r="J11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'48/62</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>50</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'3/9</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>33</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>90</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>66</v>
+      </c>
+      <c r="J12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'22/29</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'1/6</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>16</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>66</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>66</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Aníbal Moreno</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'6/10</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'26/31</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>66</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lucas Silva</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>34</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'8/8</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Facundo Colidio</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>83</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'5/13</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>38</v>
+      </c>
+      <c r="J15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'4/12</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>33</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Joaquin Freitas</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>77</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'3/12</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>25</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'14/18</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>100</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>33</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sebastián Driussi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Solidez defensiva (Permitió pocos tiros)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Baja efectividad en la definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>• Exceso de faltas cometidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J17">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -30,6 +30,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-05 8VOS VS SAN LOREN (L) LPF" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-05 4TOS VS GIMNASIA (L) LPF" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-05 SEMI VS ROSARIO C (L) LPF" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20-05 F5 VS RED BULL BR (L) CON" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1841,6 +1842,95 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -38413,6 +38503,2218 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" s="31" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" s="31" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" s="31" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" s="31" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" s="31" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" s="31" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" s="31" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" s="31" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" s="31" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" s="31" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" s="31" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" s="31" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" s="31" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" s="31" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" s="31" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" s="31" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" s="31" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" s="31" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" s="31" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" s="31" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" s="31" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" s="31" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" s="31" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Franco Armani</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'20/31</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'10/21</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>47</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Germán Pezzella</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'12/13</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>92</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'37/50</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'4/9</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>44</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Paulo Díaz</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'4/8</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'49/61</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'3/9</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>33</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Facundo González</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'7/11</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>63</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'32/44</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'1/5</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>20</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'3/6</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>50</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'1/4</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ulises Giménez</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>89</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'3/9</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>33</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'29/34</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>50</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>60</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>50</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Juan Fernando Quintero</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>60</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'51/62</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/5</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'11/13</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>84</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>100</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kevin Castaño</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>83</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'6/11</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>54</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'42/50</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>66</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Giuliano Galoppo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>73</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'5/7</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>71</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'24/34</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'3/4</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>75</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Maxi Meza</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'6/12</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'13/18</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Santiago Lencina</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'12/15</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lautaro Pereyra</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'3/12</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'9/14</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>100</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'2/5</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>40</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lucas Silva</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'4/4</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'16/18</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>100</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kendry Páez</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'5/6</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>50</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Maximiliano Salas</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>90</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'4/9</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>44</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'11/13</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>50</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ian Subiabre</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>45</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'4/10</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>40</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'8/10</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>60</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Jonathan Spiff</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Baja efectividad en la definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J17">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -34,6 +34,7 @@
     <sheet name="24-05 FINAL VS CLUB ATL (L) LPF" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="27-05 F6 VS BLOOMING (L) CON" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="17-07 F6 VS ALDOSIVI (L) CA" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="25-07 F1 VS BARRACAS CE (L) LPF" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2298,6 +2299,95 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing28.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -47312,6 +47402,2134 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'11/11</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gonzalo Montiel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'5/6</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>83</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'57/70</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>50</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'3/6</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>50</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lucas Martínez Quarta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'6/9</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>66</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'65/72</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'6/10</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>60</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nicolás Otamendi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'5/8</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>62</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'93/101</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'10/12</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>83</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Marcos Acuña</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'2/6</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>33</v>
+      </c>
+      <c r="J6" t="n">
+        <v>32</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'66/85</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'4/13</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>30</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'6/12</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>50</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lucas Silva</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'3/8</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>37</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'82/89</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'17/18</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>94</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>67</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'35/38</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>33</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fausto Vera</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'35/39</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'5/6</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>83</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lautaro Pereyra</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'14/18</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>100</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mauro Arambarri</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'9/12</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'5/8</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>100</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ángel Correa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>33</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'7/9</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'0/4</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rafael Borré</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>90</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'5/13</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>38</v>
+      </c>
+      <c r="J13" t="n">
+        <v>11</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'14/19</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Facundo Colidio</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>67</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'7/7</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'19/29</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>33</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>100</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Joaquín Freitas</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>45</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>50</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'9/12</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lucas Beltrán</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>45</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'6/8</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'9/12</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>100</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>100</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F19" s="41" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>• Baja efectividad en la definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Solidez defensiva (Permitió pocos tiros)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>• Alta precisión en el armado de juego</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J16">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -35,11 +35,10 @@
     <sheet name="27-05 F6 VS BLOOMING (L) CON" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="17-07 F6 VS ALDOSIVI (L) CA" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="25-07 F1 VS BARRACAS CE (L) LPF" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="28-01 F2 VS GIMNASIA Y (L) LPF" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="29-07 F2 VS GIMNASIA Y (V) LPF" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="02-08 F3 VS ROSARIO CEN (L) LPF" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="08-08 F4 VS TIGRE (V) LPF" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="16-08 F5 VS ARGENTINOS (L) LPF" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="29-07 F2 VS GIMNASIA Y (V) LPF" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="02-08 F3 VS ROSARIO CEN (L) LPF" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="08-08 F4 VS TIGRE (V) LPF" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="16-08 F5 VS ARGENTINOS (L) LPF" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2465,7 +2464,7 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="3429000"/>
@@ -2493,7 +2492,7 @@
     <from>
       <col>15</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="3429000"/>
@@ -2521,7 +2520,7 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="3429000"/>
@@ -2649,95 +2648,6 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4762500" cy="3429000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>15</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4762500" cy="3429000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4762500" cy="3429000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing31.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
@@ -2821,7 +2731,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing31.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2910,7 +2820,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing32.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2933,6 +2843,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2958,6 +2871,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2983,6 +2899,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -52163,7 +52082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:Z38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="4" min="1" max="1"/>
@@ -52341,7 +52260,7 @@
         <v>90</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -52350,54 +52269,54 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'15/20</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>'0/0</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>'16/18</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>'1/3</t>
+          <t>'1/6</t>
         </is>
       </c>
       <c r="T2" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -52423,7 +52342,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lucas Martínez Quarta</t>
+          <t>Gonzalo Montiel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -52435,30 +52354,30 @@
         <v>90</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>'6/7</t>
+          <t>'5/8</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>2</v>
@@ -52467,35 +52386,35 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>'75/78</t>
+          <t>'58/68</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>'0/0</t>
+          <t>'2/4</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>'3/3</t>
+          <t>'1/3</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>'0/0</t>
+          <t>'0/1</t>
         </is>
       </c>
       <c r="V3" t="n">
@@ -52508,16 +52427,16 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lautaro Rivero</t>
+          <t>Lucas Martínez Quarta</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -52529,30 +52448,30 @@
         <v>90</v>
       </c>
       <c r="D4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>'3/9</t>
+          <t>'5/6</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -52565,11 +52484,11 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>'65/76</t>
+          <t>'74/84</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -52581,7 +52500,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>'4/8</t>
+          <t>'8/16</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -52589,29 +52508,29 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>'0/1</t>
+          <t>'2/2</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gonzalo Montiel</t>
+          <t>Nicolás Otamendi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -52623,63 +52542,2280 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'5/9</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>55</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'95/102</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'6/10</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>60</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Marcos Acuña</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>61</v>
+      </c>
+      <c r="D6" t="n">
         <v>6.6</v>
       </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'1/5</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'34/39</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>66</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Facundo González</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'2/5</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'20/28</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>50</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'4/10</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'30/31</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'1/5</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>20</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lucas Silva</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>81</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'2/6</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>33</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'71/82</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>60</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ángel Correa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>71</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'5/9</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>55</v>
+      </c>
+      <c r="J10" t="n">
+        <v>17</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'17/22</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'1/7</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>14</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'4/5</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>80</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mauro Arambarri</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'2/6</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>33</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'30/32</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fausto Vera</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'1/5</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'43/44</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>100</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lautaro Pereyra</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'5/5</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Joaquín Freitas</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>90</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'9/17</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>52</v>
+      </c>
+      <c r="J14" t="n">
+        <v>19</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'23/28</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'1/5</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>20</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'3/6</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>50</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lucas Beltrán</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>61</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'1/8</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'10/13</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rafael Borré</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>50</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'7/9</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Facundo Colidio</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>'1/5</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>'7/9</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>50</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F20" s="41" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Sin aspectos negativos evidentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>• Alta precisión en el armado de juego</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J17">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'17/21</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'6/10</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gonzalo Montiel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'6/9</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>66</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'30/39</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'1/6</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>33</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lucas Martínez Quarta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'6/10</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'46/58</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'4/9</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>44</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>50</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nicolás Otamendi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'8/12</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>66</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>'1/2</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>50</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>'54/63</t>
+          <t>'48/53</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>'2/2</t>
+          <t>'0/0</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>'1/3</t>
+          <t>'1/4</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -52693,19 +54829,19 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Matías Viña</t>
+          <t>Lautaro Rivero</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -52714,62 +54850,62 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="D6" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>'0/6</t>
+          <t>'6/11</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J6" t="n">
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>'27/31</t>
+          <t>'21/30</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>'1/4</t>
+          <t>'1/2</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>'0/0</t>
+          <t>'0/2</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -52787,57 +54923,57 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aníbal Moreno</t>
+          <t>Valentín Lucero</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mediocampista</t>
+          <t>Defensor</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>'4/7</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>57</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8</v>
-      </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -52847,27 +54983,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>'73/80</t>
+          <t>'1/1</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>'0/0</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>'3/6</t>
-        </is>
-      </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -52893,7 +55029,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fausto Vera</t>
+          <t>Aníbal Moreno</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -52905,10 +55041,10 @@
         <v>90</v>
       </c>
       <c r="D8" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -52918,14 +55054,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>'5/9</t>
+          <t>'7/10</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -52941,53 +55077,53 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>'80/86</t>
+          <t>'45/52</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>'0/0</t>
+          <t>'1/2</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>'4/5</t>
+          <t>'2/3</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>'2/3</t>
+          <t>'0/1</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Juan Fernando Quintero</t>
+          <t>Fausto Vera</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -52996,13 +55132,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -53012,76 +55148,76 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>'1/2</t>
+          <t>'2/6</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>'56/71</t>
+          <t>'36/40</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>'1/4</t>
+          <t>'0/0</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>'9/16</t>
+          <t>'3/5</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>'0/1</t>
+          <t>'0/0</t>
         </is>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tomás Galván</t>
+          <t>Lautaro Pereyra</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -53090,92 +55226,92 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'2/6</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>33</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'9/16</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>'7/12</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>58</v>
-      </c>
-      <c r="J10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>'35/40</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>'2/2</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
-        <v>100</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>'3/3</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>100</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Giuliano Galoppo</t>
+          <t>Tomás Galván</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -53184,10 +55320,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D11" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -53196,80 +55332,80 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>'4/7</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>57</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'18/21</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>'1/3</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="T11" t="n">
         <v>33</v>
       </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>'13/16</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>'1/2</t>
-        </is>
-      </c>
-      <c r="T11" t="n">
-        <v>50</v>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>'0/0</t>
+          <t>'1/3</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Santiago Lencina</t>
+          <t>Juan Cruz Meza</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -53278,10 +55414,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -53294,11 +55430,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>'1/2</t>
+          <t>'0/2</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>6</v>
@@ -53313,23 +55449,23 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>'9/11</t>
+          <t>'11/12</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>'1/4</t>
+          <t>'4/7</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -53341,29 +55477,29 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>'1/2</t>
+          <t>'0/2</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sebastián Driussi</t>
+          <t>Facundo Colidio</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -53372,92 +55508,92 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>'3/6</t>
+          <t>'6/13</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>'24/28</t>
+          <t>'15/25</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>'0/1</t>
+          <t>'3/10</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>'1/2</t>
+          <t>'0/2</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>'0/0</t>
+          <t>'1/3</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Facundo Colidio</t>
+          <t>Rafael Borré</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -53466,13 +55602,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -53482,76 +55618,76 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>'6/15</t>
+          <t>'7/15</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J14" t="n">
         <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'9/17</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>100</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
         <v>2</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>'18/25</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>'2/6</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ian Subiabre</t>
+          <t>Joaquín Freitas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -53560,33 +55696,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>'1/5</t>
+          <t>'2/10</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -53595,23 +55731,23 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>'7/8</t>
+          <t>'18/21</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>'0/1</t>
+          <t>'3/5</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -53623,20 +55759,20 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>'1/4</t>
+          <t>'2/3</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -53645,7 +55781,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maximiliano Salas</t>
+          <t>Lucas Beltrán</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -53654,10 +55790,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -53670,14 +55806,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>'0/2</t>
+          <t>'0/4</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -53693,11 +55829,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>'4/4</t>
+          <t>'10/13</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -53709,11 +55845,11 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>'1/1</t>
+          <t>'0/1</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -53727,10 +55863,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -53766,7 +55902,7 @@
       </c>
       <c r="D20" s="39" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -53787,14 +55923,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>• Buen volumen de tiros al arco</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Exceso de faltas cometidas</t>
         </is>
       </c>
     </row>
@@ -53806,277 +55947,284 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29%</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>• Solidez defensiva (Permitió pocos tiros)</t>
+          <t>34%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tiros totales</t>
+          <t>Goles esperados (xG)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>• Alta precisión en el armado de juego</t>
+          <t>0.70</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tiros al arco</t>
+          <t>Tiros totales</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tiros afuera</t>
+          <t>Tiros al arco</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tiros bloqueados</t>
+          <t>Tiros afuera</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>Córners</t>
+          <t>Tiros bloqueados</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fueras de juego</t>
+          <t>Córners</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Faltas</t>
+          <t>Fueras de juego</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tarjetas amarillas</t>
+          <t>Faltas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tarjetas rojas</t>
+          <t>Tarjetas amarillas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pases totales</t>
+          <t>Tarjetas rojas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pases precisos</t>
+          <t>Pases totales</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>419</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>231</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Atajadas del arquero</t>
+          <t>Pases precisos</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>131</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quites</t>
+          <t>Atajadas del arquero</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>Intercepciones</t>
+          <t>Quites</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Despejes</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>22</t>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -54290,4369 +56438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16" customWidth="1" style="4" min="2" max="2"/>
-    <col width="16" customWidth="1" style="4" min="3" max="3"/>
-    <col width="16" customWidth="1" style="4" min="4" max="4"/>
-    <col width="38" customWidth="1" style="4" min="5" max="5"/>
-    <col width="38" customWidth="1" style="4" min="6" max="6"/>
-    <col width="16" customWidth="1" style="4" min="7" max="7"/>
-    <col width="16" customWidth="1" style="4" min="8" max="8"/>
-    <col width="16" customWidth="1" style="4" min="9" max="9"/>
-    <col width="16" customWidth="1" style="4" min="10" max="10"/>
-    <col width="16" customWidth="1" style="4" min="11" max="11"/>
-    <col width="16" customWidth="1" style="4" min="12" max="12"/>
-    <col width="16" customWidth="1" style="4" min="13" max="13"/>
-    <col width="16" customWidth="1" style="4" min="14" max="14"/>
-    <col width="16" customWidth="1" style="4" min="15" max="15"/>
-    <col width="16" customWidth="1" style="4" min="16" max="16"/>
-    <col width="16" customWidth="1" style="4" min="17" max="17"/>
-    <col width="16" customWidth="1" style="4" min="18" max="18"/>
-    <col width="16" customWidth="1" style="4" min="19" max="19"/>
-    <col width="16" customWidth="1" style="4" min="20" max="20"/>
-    <col width="16" customWidth="1" style="4" min="21" max="21"/>
-    <col width="16" customWidth="1" style="4" min="22" max="22"/>
-    <col width="16" customWidth="1" style="4" min="23" max="23"/>
-    <col width="16" customWidth="1" style="4" min="24" max="24"/>
-    <col width="16" customWidth="1" style="4" min="25" max="25"/>
-    <col width="16" customWidth="1" style="4" min="26" max="26"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Posición</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Nota SofaScore</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Quites (Tackles)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Intercepciones</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Despejes</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Duelos (Gan/Tot)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Efectividad Duelos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Pérdidas de posesión</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Faltas Cometidas</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Faltas Recibidas</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Asistencias</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Pases Clave</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Pases (Comp/Tot)</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Efectividad Pases</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Centros (Comp/Tot)</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Efectividad Centros</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Balones Largos (C/T)</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Efectividad Balones</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Regates (Exit/Tot)</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Efectividad Regates</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Goles</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Tiros Totales</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Tiros al Arco</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Tiros Afuera</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Santiago Beltrán</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Arquero</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>'0/1</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>'15/20</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>'1/6</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
-        <v>16</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Gonzalo Montiel</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Defensor</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>90</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>'5/8</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>62</v>
-      </c>
-      <c r="J3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>'58/68</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>'2/4</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>50</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>'1/3</t>
-        </is>
-      </c>
-      <c r="T3" t="n">
-        <v>33</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>'0/1</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Lucas Martínez Quarta</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Defensor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>90</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>'5/6</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>83</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>'74/84</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>'8/16</t>
-        </is>
-      </c>
-      <c r="T4" t="n">
-        <v>50</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>'2/2</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>100</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nicolás Otamendi</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Defensor</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>'5/9</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>55</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>'95/102</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>'6/10</t>
-        </is>
-      </c>
-      <c r="T5" t="n">
-        <v>60</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Marcos Acuña</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Defensor</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>61</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>'1/5</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J6" t="n">
-        <v>11</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>'34/39</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>'0/3</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>'4/6</t>
-        </is>
-      </c>
-      <c r="T6" t="n">
-        <v>66</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>'0/1</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Facundo González</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Defensor</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>29</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>'2/5</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>40</v>
-      </c>
-      <c r="J7" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>'20/28</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>'0/3</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>'0/2</t>
-        </is>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>'1/2</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>50</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Tomás Galván</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>90</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>'4/10</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>40</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>'30/31</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>96</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>'1/5</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>'0/2</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Lucas Silva</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>81</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>'2/6</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>33</v>
-      </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>'71/82</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>'3/5</t>
-        </is>
-      </c>
-      <c r="T9" t="n">
-        <v>60</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ángel Correa</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>71</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>'5/9</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>55</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>'17/22</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>'1/7</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>14</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>'4/5</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>80</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Mauro Arambarri</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>45</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>'2/6</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>33</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>'30/32</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>'0/1</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>'1/1</t>
-        </is>
-      </c>
-      <c r="T11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fausto Vera</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>45</v>
-      </c>
-      <c r="D12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>'1/5</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>'43/44</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>97</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>'1/1</t>
-        </is>
-      </c>
-      <c r="T12" t="n">
-        <v>100</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Lautaro Pereyra</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>'0/2</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>'5/5</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>'0/1</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Joaquín Freitas</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Delantero</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>90</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>'9/17</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>52</v>
-      </c>
-      <c r="J14" t="n">
-        <v>19</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>'23/28</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>'1/5</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>20</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>'3/6</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>50</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Lucas Beltrán</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Delantero</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>61</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>'1/8</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>'10/13</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>'0/2</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Rafael Borré</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Delantero</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>29</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>'1/2</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>50</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>'7/9</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>'0/1</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Facundo Colidio</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Delantero</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>19</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>'1/5</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>20</v>
-      </c>
-      <c r="J17" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>'7/9</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>'1/2</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>50</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>ESTADÍSTICAS DEL PARTIDO</t>
-        </is>
-      </c>
-      <c r="E20" s="40" t="inlineStr">
-        <is>
-          <t>PUNTOS ALTOS</t>
-        </is>
-      </c>
-      <c r="F20" s="41" t="inlineStr">
-        <is>
-          <t>PUNTOS BAJOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t>Métrica</t>
-        </is>
-      </c>
-      <c r="C21" s="39" t="inlineStr">
-        <is>
-          <t>Gimnasia y Esgrima</t>
-        </is>
-      </c>
-      <c r="D21" s="39" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>• Dominio de la posesión de balón</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>• Sin aspectos negativos evidentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Resultado</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>• Alta precisión en el armado de juego</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Posesión de balón</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Goles esperados (xG)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Tiros totales</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Tiros al arco</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Tiros afuera</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Tiros bloqueados</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Córners</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Fueras de juego</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Faltas</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Tarjetas amarillas</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Pases totales</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Pases precisos</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Atajadas del arquero</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Quites</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Intercepciones</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Despejes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D2:D17">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T17">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V17">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y17">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z17">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16" customWidth="1" style="4" min="2" max="2"/>
-    <col width="16" customWidth="1" style="4" min="3" max="3"/>
-    <col width="16" customWidth="1" style="4" min="4" max="4"/>
-    <col width="38" customWidth="1" style="4" min="5" max="5"/>
-    <col width="38" customWidth="1" style="4" min="6" max="6"/>
-    <col width="16" customWidth="1" style="4" min="7" max="7"/>
-    <col width="16" customWidth="1" style="4" min="8" max="8"/>
-    <col width="16" customWidth="1" style="4" min="9" max="9"/>
-    <col width="16" customWidth="1" style="4" min="10" max="10"/>
-    <col width="16" customWidth="1" style="4" min="11" max="11"/>
-    <col width="16" customWidth="1" style="4" min="12" max="12"/>
-    <col width="16" customWidth="1" style="4" min="13" max="13"/>
-    <col width="16" customWidth="1" style="4" min="14" max="14"/>
-    <col width="16" customWidth="1" style="4" min="15" max="15"/>
-    <col width="16" customWidth="1" style="4" min="16" max="16"/>
-    <col width="16" customWidth="1" style="4" min="17" max="17"/>
-    <col width="16" customWidth="1" style="4" min="18" max="18"/>
-    <col width="16" customWidth="1" style="4" min="19" max="19"/>
-    <col width="16" customWidth="1" style="4" min="20" max="20"/>
-    <col width="16" customWidth="1" style="4" min="21" max="21"/>
-    <col width="16" customWidth="1" style="4" min="22" max="22"/>
-    <col width="16" customWidth="1" style="4" min="23" max="23"/>
-    <col width="16" customWidth="1" style="4" min="24" max="24"/>
-    <col width="16" customWidth="1" style="4" min="25" max="25"/>
-    <col width="16" customWidth="1" style="4" min="26" max="26"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Posición</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Nota SofaScore</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Quites (Tackles)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Intercepciones</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Despejes</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Duelos (Gan/Tot)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Efectividad Duelos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Pérdidas de posesión</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Faltas Cometidas</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Faltas Recibidas</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Asistencias</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Pases Clave</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Pases (Comp/Tot)</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Efectividad Pases</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Centros (Comp/Tot)</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Efectividad Centros</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Balones Largos (C/T)</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Efectividad Balones</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Regates (Exit/Tot)</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Efectividad Regates</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Goles</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Tiros Totales</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Tiros al Arco</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Tiros Afuera</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Santiago Beltrán</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Arquero</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>'17/21</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>'6/10</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
-        <v>60</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Gonzalo Montiel</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Defensor</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>90</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>'6/9</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>66</v>
-      </c>
-      <c r="J3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>6</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>'30/39</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>'1/6</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>16</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>'1/3</t>
-        </is>
-      </c>
-      <c r="T3" t="n">
-        <v>33</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Lucas Martínez Quarta</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Defensor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>90</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>'6/10</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>60</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>'46/58</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>79</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>'4/9</t>
-        </is>
-      </c>
-      <c r="T4" t="n">
-        <v>44</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>'1/2</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>50</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nicolás Otamendi</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Defensor</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>'8/12</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>66</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>'48/53</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>'1/4</t>
-        </is>
-      </c>
-      <c r="T5" t="n">
-        <v>25</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Lautaro Rivero</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Defensor</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>84</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>'6/11</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>54</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>'21/30</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>'1/2</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>50</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>'0/2</t>
-        </is>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>'0/2</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Valentín Lucero</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Defensor</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>12</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>'1/1</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>'0/3</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Aníbal Moreno</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>90</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>'7/10</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>70</v>
-      </c>
-      <c r="J8" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>'45/52</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>'1/2</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>50</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>'2/3</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>66</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>'0/1</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fausto Vera</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>63</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>'2/6</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>33</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>'36/40</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>'3/5</t>
-        </is>
-      </c>
-      <c r="T9" t="n">
-        <v>60</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lautaro Pereyra</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>45</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>'2/6</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>33</v>
-      </c>
-      <c r="J10" t="n">
-        <v>12</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>'9/16</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>'1/1</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>'0/1</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Tomás Galván</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>45</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>'4/7</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>57</v>
-      </c>
-      <c r="J11" t="n">
-        <v>7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>'18/21</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>'1/3</t>
-        </is>
-      </c>
-      <c r="T11" t="n">
-        <v>33</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>'1/3</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>33</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Juan Cruz Meza</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Mediocampista</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>23</v>
-      </c>
-      <c r="D12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>'0/2</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>'11/12</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>91</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>'4/7</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>57</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>'0/2</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Facundo Colidio</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Delantero</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>90</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>'6/13</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>46</v>
-      </c>
-      <c r="J13" t="n">
-        <v>25</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>'15/25</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>'3/10</t>
-        </is>
-      </c>
-      <c r="R13" t="n">
-        <v>30</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>'0/2</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>'1/3</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Rafael Borré</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Delantero</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>90</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>'7/15</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>46</v>
-      </c>
-      <c r="J14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>'9/17</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>'0/1</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>'0/2</t>
-        </is>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>'1/1</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>100</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Joaquín Freitas</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Delantero</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>67</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>'2/10</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>20</v>
-      </c>
-      <c r="J15" t="n">
-        <v>13</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>'18/21</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>'3/5</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>60</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>'2/3</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>66</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Lucas Beltrán</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Delantero</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>27</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>'0/4</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>'10/13</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>'0/1</t>
-        </is>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>'0/0</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>ESTADÍSTICAS DEL PARTIDO</t>
-        </is>
-      </c>
-      <c r="E19" s="40" t="inlineStr">
-        <is>
-          <t>PUNTOS ALTOS</t>
-        </is>
-      </c>
-      <c r="F19" s="41" t="inlineStr">
-        <is>
-          <t>PUNTOS BAJOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>Métrica</t>
-        </is>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>River Plate</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>• Dominio de la posesión de balón</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>• Baja efectividad en la definición</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Resultado</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>• Buen volumen de tiros al arco</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>• Exceso de faltas cometidas</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Posesión de balón</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Goles esperados (xG)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Tiros totales</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Tiros al arco</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Tiros afuera</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Tiros bloqueados</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Córners</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Fueras de juego</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Faltas</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Tarjetas amarillas</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Tarjetas rojas</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Pases totales</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Pases precisos</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Atajadas del arquero</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Quites</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Intercepciones</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Despejes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D2:D16">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T16">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V16">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z16">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="00FFFFFF"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -60592,7 +58378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -39,6 +39,8 @@
     <sheet name="02-08 F3 VS ROSARIO CEN (L) LPF" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="08-08 F4 VS TIGRE (V) LPF" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="16-08 F5 VS ARGENTINOS (L) LPF" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="19-08 8VOS VS INDEPENDI (V) CON" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="23-08 F6 VS VÉLEZ SARSF (L) LPF" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2909,6 +2911,175 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing33.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing34.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -60600,6 +60771,4153 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'11/25</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'3/17</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>17</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lucas Martínez Quarta</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'3/7</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>42</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'37/46</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>66</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>50</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nicolás Otamendi</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'4/7</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>57</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'38/44</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'3/8</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>37</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lautaro Rivero</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'0/5</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'29/34</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'4/7</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>57</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Facundo González</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'1/8</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'39/43</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'0/5</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>66</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Valentín Lucero</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aníbal Moreno</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'3/5</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'36/44</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>33</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fausto Vera</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'1/6</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'61/67</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>50</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ángel Correa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>89</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'7/14</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'32/40</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'4/5</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>80</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'5/7</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>71</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tobías Andrada</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>78</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'4/10</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>40</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'29/32</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>33</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>62</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'2/8</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'12/17</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Thiago Almada</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>29</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'19/20</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>50</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Juan Cruz Meza</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'4/4</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rafael Borré</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>61</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'4/12</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>33</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'12/13</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Joaquín Freitas</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>50</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'4/5</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F19" s="41" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>• Sin aspectos destacados</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>• Poca generación de juego ofensivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Exceso de faltas cometidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J16">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'23/30</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'4/11</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>36</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Giovanni González</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'11/14</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>78</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'51/64</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'5/7</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>71</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>100</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lucas Martínez Quarta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'6/10</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'62/76</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'7/16</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>43</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nicolás Otamendi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'7/11</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>63</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'54/60</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'5/6</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>83</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Francisco Ortega</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'6/7</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>85</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'39/47</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'1/3</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>33</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'1/4</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>25</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aníbal Moreno</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'7/12</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>58</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'31/37</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>66</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>100</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tobías Andrada</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'5/10</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'62/72</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'6/7</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>85</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>50</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Thiago Almada</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'3/7</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>42</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'64/75</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'1/4</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>25</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'7/8</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>87</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>100</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ángel Correa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>70</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'4/13</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'33/37</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>100</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'2/7</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>28</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lautaro Pereyra</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'3/4</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Joaquín Freitas</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>84</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'3/7</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>42</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'24/36</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lucas Beltrán</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>84</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'5/13</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>38</v>
+      </c>
+      <c r="J13" t="n">
+        <v>11</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'17/21</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>100</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Rafael Borré</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'2/5</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>40</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'3/4</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sebastián Driussi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'4/4</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F18" s="41" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D19" s="39" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>• Baja efectividad en la definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J15">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K15">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z15">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Base_Datos_River_2026.xlsx
+++ b/Base_Datos_River_2026.xlsx
@@ -41,6 +41,8 @@
     <sheet name="16-08 F5 VS ARGENTINOS (L) LPF" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="19-08 8VOS VS INDEPENDI (V) CON" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="23-08 F6 VS VÉLEZ SARSF (L) LPF" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="26-08 8VOS VS INDEPENDI (L) CON" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="30-08 F7 VS BANFIELD (V) LPF" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -3023,6 +3025,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3048,6 +3053,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3057,6 +3065,178 @@
       <col>7</col>
       <colOff>0</colOff>
       <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing35.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing36.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4762500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="3429000"/>
@@ -64918,6 +65098,4450 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'15/17</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'6/8</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>75</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lucas Martínez Quarta</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'4/9</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>44</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'49/59</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>100</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'4/11</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>36</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nicolás Otamendi</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'7/10</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>70</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'58/67</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'13/18</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>72</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Marcos Acuña</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'5/12</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>41</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'56/61</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'2/9</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>22</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'3/4</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>75</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gonzalo Montiel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>76</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'1/5</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'43/58</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'1/4</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>25</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'3/6</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>50</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Facundo González</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>66</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'15/19</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>50</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ángel Correa</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'8/21</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>38</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'29/34</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'3/3</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>100</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'3/6</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>50</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Thiago Almada</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'5/9</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>55</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'47/52</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'3/6</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>50</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'5/5</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'4/5</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>80</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Aníbal Moreno</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>82</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'3/7</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>42</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'39/45</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'5/7</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>71</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tobías Andrada</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>76</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'3/4</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'69/72</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/4</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'10/10</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>62</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'1/4</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'28/34</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>50</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fausto Vera</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>28</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>66</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'20/22</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Juan Cruz Meza</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'7/8</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>50</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sebastián Driussi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>62</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'0/4</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'17/23</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rafael Borré</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'7/10</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>70</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'4/8</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Joaquín Freitas</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>66</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>'7/7</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>100</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F20" s="41" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• Baja efectividad en la definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>• Buen volumen de tiros al arco</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>• Exceso de faltas cometidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>• Alta precisión en el armado de juego</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J17">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16" customWidth="1" style="4" min="3" max="3"/>
+    <col width="16" customWidth="1" style="4" min="4" max="4"/>
+    <col width="38" customWidth="1" style="4" min="5" max="5"/>
+    <col width="38" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="15" max="15"/>
+    <col width="16" customWidth="1" style="4" min="16" max="16"/>
+    <col width="16" customWidth="1" style="4" min="17" max="17"/>
+    <col width="16" customWidth="1" style="4" min="18" max="18"/>
+    <col width="16" customWidth="1" style="4" min="19" max="19"/>
+    <col width="16" customWidth="1" style="4" min="20" max="20"/>
+    <col width="16" customWidth="1" style="4" min="21" max="21"/>
+    <col width="16" customWidth="1" style="4" min="22" max="22"/>
+    <col width="16" customWidth="1" style="4" min="23" max="23"/>
+    <col width="16" customWidth="1" style="4" min="24" max="24"/>
+    <col width="16" customWidth="1" style="4" min="25" max="25"/>
+    <col width="16" customWidth="1" style="4" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nota SofaScore</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quites (Tackles)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Duelos (Gan/Tot)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Efectividad Duelos</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Pérdidas de posesión</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Faltas Cometidas</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Faltas Recibidas</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Pases Clave</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Pases (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Efectividad Pases</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Centros (Comp/Tot)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Efectividad Centros</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Balones Largos (C/T)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Efectividad Balones</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Regates (Exit/Tot)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Efectividad Regates</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Goles</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Tiros Totales</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Tiros al Arco</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Tiros Afuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Santiago Beltrán</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arquero</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'19/30</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'9/20</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>45</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nicolás Otamendi</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'8/9</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>88</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'39/48</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>66</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>100</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lucas Martínez Quarta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>88</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'1/2</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'33/43</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'1/8</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>12</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>100</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Marcos Acuña</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>82</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'5/6</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>83</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'29/37</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'2/3</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>66</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>100</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gonzalo Montiel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>69</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'5/7</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>71</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'38/43</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>66</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Giovanni González</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>21</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'8/9</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Francisco Ortega</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'5/5</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lautaro Rivero</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Defensor</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fausto Vera</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>'8/11</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>72</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'45/53</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>66</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>100</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Thiago Almada</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'3/11</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>27</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'54/63</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0/3</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'4/4</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ángel Correa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>90</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>'4/12</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>33</v>
+      </c>
+      <c r="J12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'48/53</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>'0/4</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>'4/5</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>80</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>'1/4</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tomás Galván</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>90</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'4/7</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>57</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'35/41</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tobías Andrada</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>88</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>'2/9</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>22</v>
+      </c>
+      <c r="J14" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'42/49</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>'2/4</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>50</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mauro Arambarri</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mediocampista</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'4/6</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>'0/1</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>'0/2</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sebastián Driussi</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>69</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>'2/6</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>33</v>
+      </c>
+      <c r="J16" t="n">
+        <v>12</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'13/19</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>'2/2</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>100</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lucas Beltrán</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Delantero</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>'6/8</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>'1/1</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>100</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>'0/0</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>ESTADÍSTICAS DEL PARTIDO</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>PUNTOS ALTOS</t>
+        </is>
+      </c>
+      <c r="F20" s="41" t="inlineStr">
+        <is>
+          <t>PUNTOS BAJOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>• Dominio de la posesión de balón</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>• El rival llegó con facilidad al arco</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>• Buen volumen de tiros al arco</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J17">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y17">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
